--- a/results/385_1/mutations_per_branch.xlsx
+++ b/results/385_1/mutations_per_branch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pythoncourse42026\Final-project-BCR-Lineage-Tracer\results\385_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE79949B-5DB6-46E6-9A93-4234670F4BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD1200D-DDA9-4AF1-9E49-7F0609FD7756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1222,7 +1222,7 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>228057</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>6456</xdr:rowOff>
+      <xdr:rowOff>9482</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
@@ -1601,71 +1601,6 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>7582</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>23510</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>154462</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>18788</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId34">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="43" name="דיו 42">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3B019A5-994F-35DC-997C-C1D8C86F2453}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="18652770" y="6048073"/>
-            <a:ext cx="146880" cy="177840"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="43" name="דיו 42">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3B019A5-994F-35DC-997C-C1D8C86F2453}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="18617130" y="6012433"/>
-              <a:ext cx="218520" cy="249480"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1898,34 +1833,6 @@
     </inkml:brush>
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1,'3'0,"5"0,3 0,4 0,2 0,1 0,2 0,-1 0,1 0,-4 0</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink17.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-06-03T12:59:25.760"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.2" units="cm"/>
-      <inkml:brushProperty name="height" value="0.2" units="cm"/>
-      <inkml:brushProperty name="color" value="#849398"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">4498 3151 24575,'2'34'0,"9"54"0,-1-21 0,-4-34 0,1 0 0,2 0 0,26 60 0,-12-32 0,-21-58 0,-1 0 0,1 0 0,0 0 0,0 0 0,0 0 0,1 0 0,-1-1 0,1 1 0,-1-1 0,1 1 0,0-1 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,1-1 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1-1 0,3 0 0,15 2 0,-1-2 0,1 0 0,22-4 0,-1 1 0,35 2-1365</inkml:trace>
 </inkml:ink>
 </file>
 
